--- a/data/Mau_GoogleSheet_Thi_Tin12_5Sheet.xlsx
+++ b/data/Mau_GoogleSheet_Thi_Tin12_5Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8CFACE-9C94-4318-BA65-3206CEBEE56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4C9165-2A35-43CA-93C6-222841141B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HUONG_DAN" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="647">
   <si>
     <t>Mục</t>
   </si>
@@ -1979,12 +1979,6 @@
   </si>
   <si>
     <t>0,5</t>
-  </si>
-  <si>
-    <t>8/10/2026:04:00</t>
-  </si>
-  <si>
-    <t>12/10/2026:23:30</t>
   </si>
 </sst>
 </file>
@@ -2684,7 +2678,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>573</v>
       </c>
@@ -6822,7 +6816,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -6840,11 +6835,11 @@
       <c r="A2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>648</v>
+      <c r="B2" s="4">
+        <v>46244</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46366</v>
       </c>
     </row>
   </sheetData>
